--- a/core/utils/docs_proj_p/distgradeunificada12.xlsx
+++ b/core/utils/docs_proj_p/distgradeunificada12.xlsx
@@ -622,7 +622,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="-0.25"/>
-        <bgColor rgb="FF333F50"/>
+        <bgColor rgb="FF333F4F"/>
       </patternFill>
     </fill>
     <fill>
@@ -695,59 +695,59 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -818,7 +818,7 @@
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF2F5597"/>
-      <rgbColor rgb="FF333F50"/>
+      <rgbColor rgb="FF333F4F"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -2573,11 +2573,21 @@
       <c r="F44" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
+      <c r="G44" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H44" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I44" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="J44" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="K44" s="11" t="n">
+        <v>12</v>
+      </c>
       <c r="L44" s="11"/>
       <c r="M44" s="11"/>
       <c r="N44" s="11"/>
@@ -2643,11 +2653,21 @@
       <c r="F46" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="11"/>
+      <c r="G46" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H46" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="I46" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="J46" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K46" s="11" t="n">
+        <v>21</v>
+      </c>
       <c r="L46" s="11"/>
       <c r="M46" s="11"/>
       <c r="N46" s="11"/>
@@ -2771,11 +2791,21 @@
       <c r="F50" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="11"/>
-      <c r="J50" s="11"/>
-      <c r="K50" s="11"/>
+      <c r="G50" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H50" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="I50" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="J50" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="K50" s="11" t="n">
+        <v>12</v>
+      </c>
       <c r="L50" s="11"/>
       <c r="M50" s="11"/>
       <c r="N50" s="11"/>
